--- a/data/trans_camb/P42-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P42-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,02</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,12</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,94; 10,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,19; 8,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,32; 5,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 10,21</t>
+          <t>1,94; 10,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 8,75</t>
+          <t>0,19; 8,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 5,13</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 10,21</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 8,75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-4,25; 5,13</t>
+          <t>-4,32; 5,0</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,13%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,12; 11,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,18; 9,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,67; 5,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,77</t>
+          <t>2,12; 11,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 10,09</t>
+          <t>0,18; 9,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,86</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 11,77</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,66; 10,09</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-4,57; 5,86</t>
+          <t>-4,67; 5,74</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,76</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,38</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,76</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10,38</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4,9</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,19; 13,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,43; 14,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,23; 9,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 13,13</t>
+          <t>4,19; 13,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 14,43</t>
+          <t>6,43; 14,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 10,07</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,27; 13,13</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,02; 14,43</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 10,07</t>
+          <t>-0,23; 9,38</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,83; 15,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,22; 18,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,17; 11,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 15,89</t>
+          <t>4,83; 15,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 17,57</t>
+          <t>7,22; 18,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 12,32</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,87; 15,89</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6,88; 17,57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 12,32</t>
+          <t>-0,17; 11,55</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,53</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,53</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,58</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1,95</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,36; 15,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,73; 16,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,75; 10,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 15,2</t>
+          <t>2,36; 15,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 17,09</t>
+          <t>2,73; 16,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 9,45</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,27; 15,2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3,29; 17,09</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 9,45</t>
+          <t>-5,75; 10,47</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,78; 19,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,14; 20,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,56; 13,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 19,47</t>
+          <t>2,78; 19,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 21,6</t>
+          <t>3,14; 20,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 11,97</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2,56; 19,47</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>3,87; 21,6</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-5,74; 11,97</t>
+          <t>-6,56; 13,07</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-15,74</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-15,74</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,58</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10,11</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>-15,74</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,96; 13,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,94; 14,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-49,59; 9,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,82</t>
+          <t>5,96; 13,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 14,26</t>
+          <t>6,94; 14,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 8,93</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,23; 13,82</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6,84; 14,26</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-54,39; 8,93</t>
+          <t>-49,59; 9,33</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-19,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-19,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>-19,66%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,3; 17,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,44; 18,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-62,41; 11,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,53; 17,69</t>
+          <t>7,3; 17,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 18,44</t>
+          <t>8,44; 18,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 11,2</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,53; 17,69</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8,31; 18,44</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-67,53; 11,2</t>
+          <t>-62,41; 11,77</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,85</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3,68</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,32; 7,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,41; 7,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,52; 8,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 7,95</t>
+          <t>-0,32; 7,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,46</t>
+          <t>-0,41; 7,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 8,81</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-0,07; 7,95</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-0,55; 7,46</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 8,81</t>
+          <t>-0,52; 8,81</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>4,36%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,38; 9,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,49; 8,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,57; 10,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,72</t>
+          <t>-0,38; 9,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 9,24</t>
+          <t>-0,49; 8,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 10,77</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-0,08; 9,72</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 9,24</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 10,77</t>
+          <t>-0,57; 10,97</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,87</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,24</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>2,72</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,45; 11,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,46; 10,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,79; 7,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,69</t>
+          <t>4,45; 11,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,99</t>
+          <t>3,46; 10,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 7,36</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,32; 11,69</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3,4; 10,99</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-2,13; 7,36</t>
+          <t>-1,79; 7,6</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,16; 16,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,78; 15,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,45; 10,95</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,89; 16,85</t>
+          <t>6,16; 16,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,7; 15,89</t>
+          <t>4,78; 15,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 10,49</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>5,89; 16,85</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>4,7; 15,89</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>-3,02; 10,49</t>
+          <t>-2,45; 10,95</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>-0,44</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,35; 10,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,31; 9,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,32; 6,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,85</t>
+          <t>6,35; 10,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,87</t>
+          <t>6,31; 9,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 6,43</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6,38; 9,85</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>6,39; 9,87</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-19,25; 6,43</t>
+          <t>-16,32; 6,69</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-0,55%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>-0,55%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,93; 12,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,83; 12,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,58; 8,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,66</t>
+          <t>7,93; 12,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,67</t>
+          <t>7,83; 12,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 8,18</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>8,01; 12,66</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>7,95; 12,67</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-24,29; 8,18</t>
+          <t>-20,58; 8,47</t>
         </is>
       </c>
     </row>
@@ -2131,13 +1683,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P42-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P42-Clase-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 10,19</t>
+          <t>1,91; 9,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,35</t>
+          <t>0,61; 8,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,0</t>
+          <t>-4,95; 4,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 10,19</t>
+          <t>1,91; 9,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,35</t>
+          <t>0,61; 8,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,0</t>
+          <t>-4,95; 4,43</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>-0,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>-0,21%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 11,7</t>
+          <t>2,11; 11,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,61</t>
+          <t>0,68; 10,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 5,74</t>
+          <t>-5,36; 5,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 11,7</t>
+          <t>2,11; 11,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,61</t>
+          <t>0,68; 10,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 5,74</t>
+          <t>-5,36; 5,09</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>5,26</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 13,1</t>
+          <t>4,27; 13,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 14,84</t>
+          <t>6,38; 14,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,38</t>
+          <t>0,75; 10,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 13,1</t>
+          <t>4,27; 13,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 14,84</t>
+          <t>6,38; 14,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,38</t>
+          <t>0,75; 10,22</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,82</t>
+          <t>4,85; 16,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 18,01</t>
+          <t>7,25; 17,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 11,55</t>
+          <t>0,81; 12,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,82</t>
+          <t>4,85; 16,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 18,01</t>
+          <t>7,25; 17,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 11,55</t>
+          <t>0,81; 12,43</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 15,47</t>
+          <t>1,99; 15,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 16,06</t>
+          <t>2,34; 16,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 10,47</t>
+          <t>-6,82; 8,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 15,47</t>
+          <t>1,99; 15,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 16,06</t>
+          <t>2,34; 16,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 10,47</t>
+          <t>-6,82; 8,79</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 19,63</t>
+          <t>2,28; 19,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 20,36</t>
+          <t>2,94; 20,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 13,07</t>
+          <t>-7,75; 11,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 19,63</t>
+          <t>2,28; 19,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 20,36</t>
+          <t>2,94; 20,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 13,07</t>
+          <t>-7,75; 11,14</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-15,74</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,74</t>
+          <t>8,0</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,33</t>
+          <t>5,68; 13,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,26</t>
+          <t>6,45; 13,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 9,33</t>
+          <t>4,44; 11,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,33</t>
+          <t>5,68; 13,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,26</t>
+          <t>6,45; 13,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 9,33</t>
+          <t>4,44; 11,84</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,66%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,66%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 17,13</t>
+          <t>6,98; 17,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,52</t>
+          <t>7,8; 17,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 11,77</t>
+          <t>5,42; 15,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 17,13</t>
+          <t>6,98; 17,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,52</t>
+          <t>7,8; 17,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 11,77</t>
+          <t>5,42; 15,28</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,89</t>
+          <t>-0,1; 7,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,33</t>
+          <t>-0,6; 7,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 8,81</t>
+          <t>-3,53; 4,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,89</t>
+          <t>-0,1; 7,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,33</t>
+          <t>-0,6; 7,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 8,81</t>
+          <t>-3,53; 4,67</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1334,39 +1334,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,72</t>
+          <t>-0,12; 9,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,88</t>
+          <t>-0,73; 9,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,97</t>
+          <t>-4,09; 5,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,72</t>
+          <t>-0,12; 9,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,88</t>
+          <t>-0,73; 9,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,97</t>
+          <t>-4,09; 5,73</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,02</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,18</t>
+          <t>4,29; 11,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,59</t>
+          <t>3,46; 10,85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 7,6</t>
+          <t>-2,96; 6,84</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,18</t>
+          <t>4,29; 11,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,59</t>
+          <t>3,46; 10,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 7,6</t>
+          <t>-2,96; 6,84</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,16; 16,12</t>
+          <t>5,88; 16,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4,78; 15,46</t>
+          <t>4,7; 15,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 10,95</t>
+          <t>-4,09; 9,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,16; 16,12</t>
+          <t>5,88; 16,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,78; 15,46</t>
+          <t>4,7; 15,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 10,95</t>
+          <t>-4,09; 9,78</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>4,82</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,02</t>
+          <t>6,48; 9,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,31; 9,84</t>
+          <t>6,41; 9,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 6,69</t>
+          <t>2,89; 6,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,02</t>
+          <t>6,48; 9,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,31; 9,84</t>
+          <t>6,41; 9,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 6,69</t>
+          <t>2,89; 6,94</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-0,55%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0,55%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,89</t>
+          <t>8,09; 12,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,6</t>
+          <t>8,0; 12,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 8,47</t>
+          <t>3,62; 8,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,89</t>
+          <t>8,09; 12,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,6</t>
+          <t>8,0; 12,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 8,47</t>
+          <t>3,62; 8,89</t>
         </is>
       </c>
     </row>
